--- a/docs/直播数据管理设计方案/巨量营销-智擎版表头字段标准.xlsx
+++ b/docs/直播数据管理设计方案/巨量营销-智擎版表头字段标准.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2aa682800de442c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6e17d985abe4891"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3502,7 +3502,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -3514,6 +3514,12 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -3886,242 +3892,242 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="28.799999237060547" customHeight="1">
-      <x:c r="A5" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>19</x:v>
+    <x:row r="5" ht="120" customHeight="1">
+      <x:c r="A5" s="5" t="str">
+        <x:v>维度</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>advertiser_id</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>账户ID</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>账户维度。来源：请求参数 advertiser_id，随结果保存；不是返回指标。建议以字符串保存长ID，避免精度丢失。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="43.20000076293945" customHeight="1">
-      <x:c r="A6" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>22</x:v>
+    <x:row r="6" ht="120" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>维度</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>account_name</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>账户名称</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>账户维度。来源：账户主数据，按 advertiser_id 关联。统一字段名沿用试点账户清单 account_name；不是本报表接口返回字段。</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="43.20000076293945" customHeight="1">
-      <x:c r="A7" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>25</x:v>
+    <x:row r="7" ht="120" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>维度</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>account_type</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>账户类型</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>账户维度。来源：试点账户清单/账户配置，如直投、短视频投放。为业务分类，按账户及生效时间关联，不按名称推断。</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="16" customHeight="1">
-      <x:c r="A8" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>28</x:v>
+    <x:row r="8" ht="120" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>维度</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>stat_platform</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>统计平台</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>账户维度。来源：账户配置/采集上下文。统计平台取值如巨量营销-智擎版、巨量营销-旧版、巨量千川；不是接口返回指标。</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="16" customHeight="1">
+    <x:row r="9" ht="28.799999237060547" customHeight="1">
       <x:c r="A9" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="16" customHeight="1">
+    <x:row r="10" ht="43.20000076293945" customHeight="1">
       <x:c r="A10" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="129.60000610351562" customHeight="1">
+    <x:row r="11" ht="43.20000076293945" customHeight="1">
       <x:c r="A11" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="129.60000610351562" customHeight="1">
+    <x:row r="12" ht="16" customHeight="1">
       <x:c r="A12" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="57.599998474121094" customHeight="1">
+    <x:row r="13" ht="16" customHeight="1">
       <x:c r="A13" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="144" customHeight="1">
+    <x:row r="14" ht="16" customHeight="1">
       <x:c r="A14" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="28.799999237060547" customHeight="1">
+    <x:row r="15" ht="129.60000610351562" customHeight="1">
       <x:c r="A15" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="16" customHeight="1">
+    <x:row r="16" ht="129.60000610351562" customHeight="1">
       <x:c r="A16" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="28.799999237060547" customHeight="1">
+    <x:row r="17" ht="57.599998474121094" customHeight="1">
       <x:c r="A17" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E17" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="28.799999237060547" customHeight="1">
+    <x:row r="18" ht="144" customHeight="1">
       <x:c r="A18" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="28.799999237060547" customHeight="1">
@@ -4129,33 +4135,33 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E19" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="129.60000610351562" customHeight="1">
+    <x:row r="20" ht="16" customHeight="1">
       <x:c r="A20" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="28.799999237060547" customHeight="1">
@@ -4163,16 +4169,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E21" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="28.799999237060547" customHeight="1">
@@ -4180,16 +4186,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E22" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="28.799999237060547" customHeight="1">
@@ -4197,33 +4203,33 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E23" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="28.799999237060547" customHeight="1">
+    <x:row r="24" ht="129.60000610351562" customHeight="1">
       <x:c r="A24" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E24" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="28.799999237060547" customHeight="1">
@@ -4231,16 +4237,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="28.799999237060547" customHeight="1">
@@ -4248,33 +4254,33 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E26" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="43.20000076293945" customHeight="1">
+    <x:row r="27" ht="28.799999237060547" customHeight="1">
       <x:c r="A27" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E27" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="28.799999237060547" customHeight="1">
@@ -4282,16 +4288,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C28" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E28" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="28.799999237060547" customHeight="1">
@@ -4299,33 +4305,33 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B29" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C29" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E29" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="57.599998474121094" customHeight="1">
+    <x:row r="30" ht="28.799999237060547" customHeight="1">
       <x:c r="A30" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C30" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E30" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="43.20000076293945" customHeight="1">
@@ -4333,151 +4339,219 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C31" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E31" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="57.599998474121094" customHeight="1">
+    <x:row r="32" ht="28.799999237060547" customHeight="1">
       <x:c r="A32" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C32" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E32" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="57.599998474121094" customHeight="1">
+    <x:row r="33" ht="28.799999237060547" customHeight="1">
       <x:c r="A33" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B33" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C33" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E33" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="28.799999237060547" customHeight="1">
+    <x:row r="34" ht="57.599998474121094" customHeight="1">
       <x:c r="A34" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E34" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="28.799999237060547" customHeight="1">
+    <x:row r="35" ht="43.20000076293945" customHeight="1">
       <x:c r="A35" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B35" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E35" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="28.799999237060547" customHeight="1">
+    <x:row r="36" ht="57.599998474121094" customHeight="1">
       <x:c r="A36" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B36" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C36" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E36" s="4" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="57.599998474121094" customHeight="1">
+      <x:c r="A37" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="28.799999237060547" customHeight="1">
+      <x:c r="A38" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B38" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C38" s="4" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D38" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E38" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="28.799999237060547" customHeight="1">
+      <x:c r="A39" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="28.799999237060547" customHeight="1">
+      <x:c r="A40" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B40" s="4" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C40" s="4" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E40" s="4" t="s">
         <x:v>111</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="135" customHeight="1">
-      <x:c r="A37" s="3" t="str">
+    <x:row r="41" ht="135" customHeight="1">
+      <x:c r="A41" s="3" t="str">
         <x:v>指标</x:v>
       </x:c>
-      <x:c r="B37" s="4" t="str">
+      <x:c r="B41" s="4" t="str">
         <x:v>deep_convert_cnt</x:v>
       </x:c>
-      <x:c r="C37" s="4" t="str">
+      <x:c r="C41" s="4" t="str">
         <x:v>深度转化数</x:v>
       </x:c>
-      <x:c r="D37" s="4" t="str">
+      <x:c r="D41" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
-      <x:c r="E37" s="4" t="str">
+      <x:c r="E41" s="4" t="str">
         <x:v>将深度转化数记录在转化事件发生的时间上。建议客户考核深度转化成本时参考“深度转化数（计费时间）”例如您投放的内容在早上8点进行了展示和点击，用户晚上19点发生了激活行为，我们会把激活数披露在晚上19点。</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="60" customHeight="1">
-      <x:c r="A38" s="3" t="str">
+    <x:row r="42" ht="60" customHeight="1">
+      <x:c r="A42" s="3" t="str">
         <x:v>指标</x:v>
       </x:c>
-      <x:c r="B38" s="4" t="str">
+      <x:c r="B42" s="4" t="str">
         <x:v>deep_convert_cost</x:v>
       </x:c>
-      <x:c r="C38" s="4" t="str">
+      <x:c r="C42" s="4" t="str">
         <x:v>深度转化成本(元)</x:v>
       </x:c>
-      <x:c r="D38" s="4" t="str">
+      <x:c r="D42" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
-      <x:c r="E38" s="4" t="str">
+      <x:c r="E42" s="4" t="str">
         <x:v>计算公式是：消耗（元）/深度转化数。当天数据可能会有波动，次日早8点后稳定。</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="60" customHeight="1">
-      <x:c r="A39" s="3" t="str">
+    <x:row r="43" ht="60" customHeight="1">
+      <x:c r="A43" s="3" t="str">
         <x:v>指标</x:v>
       </x:c>
-      <x:c r="B39" s="4" t="str">
+      <x:c r="B43" s="4" t="str">
         <x:v>deep_convert_rate</x:v>
       </x:c>
-      <x:c r="C39" s="4" t="str">
+      <x:c r="C43" s="4" t="str">
         <x:v>深度转化率</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="str">
+      <x:c r="D43" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
-      <x:c r="E39" s="4" t="str">
+      <x:c r="E43" s="4" t="str">
         <x:v>计算公式是：深度转化数/转化数*100%。当天数据可能会有波动，次日早8点后稳定。</x:v>
       </x:c>
     </x:row>
